--- a/reports/滨江一号桩基工程_2026-06-21_桩基校核报告.xlsx
+++ b/reports/滨江一号桩基工程_2026-06-21_桩基校核报告.xlsx
@@ -35,7 +35,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -58,12 +58,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFE699"/>
         <bgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-        <bgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -111,9 +105,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -481,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -530,7 +521,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
@@ -540,7 +531,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-06-21 04:52:30</t>
+          <t>2026-06-21 05:02:51</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -575,7 +566,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="n"/>
@@ -589,63 +580,67 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>提示</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>按问题类型统计</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>按问题类型统计</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>问题类型</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>严重程度</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>问题类型</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>严重程度</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>混凝土方量差异超限</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>警告</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>混凝土方量差异超限</t>
+          <t>实际孔深不足</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>警告</t>
+          <t>严重</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -658,7 +653,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>实际孔深不足</t>
+          <t>桩号为空</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -667,7 +662,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n"/>
@@ -691,64 +686,10 @@
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>桩号为空</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>成孔到灌注间隔过长</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>警告</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>关键字段缺失</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>提示</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-    </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A10:C10"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A11:C11"/>
     <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -761,569 +702,730 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
+          <t>问题编号</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>严重程度</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>问题类型</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>文件名</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>桩号</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>行号</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>疑似原因</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>建议复核项</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>详细信息</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>是否整改</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>整改说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>HOL-F0C5CD3F</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>严重</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>实际孔深不足</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>2026-06-21_三区桩基记录.xlsx</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>ZH2</t>
         </is>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="G2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>实际孔深 24.80m 低于设计桩长 25.00m，短少 0.20m</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>复核孔深测量记录，确认是否存在测绳误差或孔底沉渣过厚</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>第 3 行，差值 -0.20m</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr"/>
       <c r="K2" s="5" t="inlineStr"/>
+      <c r="L2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>HOL-D66C98A9</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>严重</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>实际孔深不足</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-21_五区自定义表头.csv</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>ZH21</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>实际孔深 24.60m 低于设计桩长 25.00m，短少 0.40m</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>复核孔深测量记录，确认是否存在测绳误差或孔底沉渣过厚</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>第 3 行，差值 -0.40m</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>HOL-6D571FE2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>实际孔深不足</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2026-06-21_四区异常记录.csv</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>ZK18</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="G4" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>实际孔深 26.80m 低于设计桩长 27.00m，短少 0.20m</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>复核孔深测量记录，确认是否存在测绳误差或孔底沉渣过厚</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>第 7 行，差值 -0.20m</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>PIL-A12CAF7E</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>桩号缺失</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>(汇总)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>(批量)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>应有 120 根桩，实际有效记录 18 根，缺少 102 根</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>对照桩位布置图检查是否漏报，或与现场施工日志核对</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>差 102 根</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr"/>
+      <c r="L5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>PIL-D889FDBD</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>桩号缺失</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>(汇总)</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>(连号检查)</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>桩号范围 ZK1~ZK120 之间存在断号: ZK4, ZK5, ZK10, ZK11, ZK12, ZK14, ZK17, ZK19, ZK23, ZK25 等共 103 根</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>检查断号桩是否漏报或设计变更取消</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>缺失 103 根</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>PIL-16373E34</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>桩号为空</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-21_五区自定义表头.csv</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>(空)</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>该行桩号为空（设计桩长=20.0, 桩径=800.0, 成孔=06-21 15:30, 灌注=06-21 21:00），已有数据填写但漏了桩号</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>补填桩号后再审；如为汇总/空行请删除整行</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>第 5 行</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>PIL-209D5686</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>桩号为空</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-21_四区异常记录.csv</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>(空)</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>该行桩号为空（设计桩长=28.0, 实际孔深=28.3, 方量=9.6, 理论方量=9.4, 桩径=800.0, 成孔=06-21 09:10, 灌注=06-21 15:00），已有数据填写但漏了桩号</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>补填桩号后再审；如为汇总/空行请删除整行</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>第 3 行</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>PIL-7946069F</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>严重</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>桩号缺失</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>(汇总)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>(批量)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>应有 120 根桩，实际有效记录 13 根，缺少 107 根</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>对照桩位布置图检查是否漏报，或与现场施工日志核对</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>差 107 根</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>桩号为空</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-21_四区异常记录.csv</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>(空)</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>该行桩号为空（设计桩长=24.0, 成孔=06-21 15:45, 灌注=06-21 21:00），已有数据填写但漏了桩号</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>补填桩号后再审；如为汇总/空行请删除整行</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>第 6 行</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>VOL-CF304AB8</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>警告</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>混凝土方量差异超限</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-21_三区桩基记录.xlsx</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>ZH2</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>混凝土记录方量 8.80m³，理论方量 8.20m³，超灌 7.3%</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>复核砼小票累计方量，检查是否存在扩孔、坍孔或记录偏差</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>第 3 行，偏差 +7.3%，阈值 ±5%</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>VOL-03C3853F</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>警告</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>混凝土方量差异超限</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-21_五区自定义表头.csv</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>ZH21</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>混凝土记录方量 8.80m³，理论方量 8.20m³，超灌 7.3%</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>复核砼小票累计方量，检查是否存在扩孔、坍孔或记录偏差</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>第 3 行，偏差 +7.3%，阈值 ±5%</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>VOL-77EFB3E8</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>警告</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>混凝土方量差异超限</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-21_五区自定义表头.csv</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>ZH24</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>混凝土记录方量 9.20m³，理论方量 8.70m³，超灌 5.7%</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>复核砼小票累计方量，检查是否存在扩孔、坍孔或记录偏差</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>第 6 行，偏差 +5.7%，阈值 ±5%</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>VOL-A113B7A2</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>警告</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>混凝土方量差异超限</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-21_四区异常记录.csv</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>ZK15</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>桩号缺失</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>(汇总)</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>(连号检查)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>桩号范围 ZK1~ZK120 之间存在断号: ZK4, ZK5, ZK10, ZK11, ZK14, ZK17, ZK19, ZK20, ZK21, ZK22 等共 108 根</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>检查断号桩是否漏报或设计变更取消</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>缺失 108 根</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>混凝土记录方量 10.80m³，理论方量 15.08m³，少灌 28.4%</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>复核砼小票累计方量，检查是否存在扩孔、坍孔或记录偏差</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>第 4 行，偏差 -28.4%，阈值 ±5%</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>VOL-FEA0534E</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>警告</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>混凝土方量差异超限</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-21_四区异常记录.csv</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>ZK16</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>桩号为空</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-21_四区异常记录.csv</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>(空)</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>该行桩号为空（设计桩长=28.0, 方量=9.6），其他字段已填写，疑似漏填桩号</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>补填桩号后再审；如为汇总/空行请删除整行</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>第 3 行</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>桩号为空</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-21_四区异常记录.csv</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>(空)</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>该行桩号为空（设计桩长=24.0），其他字段已填写，疑似漏填桩号</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>补填桩号后再审；如为汇总/空行请删除整行</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>第 6 行</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr"/>
-      <c r="K7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>警告</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>成孔到灌注间隔过长</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-21_二区桩基记录.csv</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>ZK12</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>灌注时间 2026-06-21 19:00 早于成孔时间 2026-06-22 08:00，时间逻辑矛盾</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>检查成孔时间和灌注时间填报是否颠倒或格式错误</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>第 7 行</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>警告</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>混凝土方量差异超限</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-21_三区桩基记录.xlsx</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>ZH2</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>混凝土记录方量 8.80m³，理论方量 8.20m³，超灌 7.3%</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>混凝土记录方量 8.90m³，理论方量 13.07m³，少灌 31.9%</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>复核砼小票累计方量，检查是否存在扩孔、坍孔或记录偏差</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>第 3 行，偏差 +7.3%，阈值 ±5%</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr"/>
-      <c r="K9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>警告</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>混凝土方量差异超限</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-21_四区异常记录.csv</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>ZK15</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>混凝土记录方量 10.80m³，理论方量 15.08m³，少灌 28.4%</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>复核砼小票累计方量，检查是否存在扩孔、坍孔或记录偏差</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>第 4 行，偏差 -28.4%，阈值 ±5%</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>警告</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>混凝土方量差异超限</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-21_四区异常记录.csv</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>ZK16</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>混凝土记录方量 8.90m³，理论方量 13.07m³，少灌 31.9%</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>复核砼小票累计方量，检查是否存在扩孔、坍孔或记录偏差</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>第 5 行，偏差 -31.9%，阈值 ±5%</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>提示</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>关键字段缺失</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-21_二区桩基记录.csv</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>ZK12</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>关键字段缺失: 实际孔深</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>补充缺失数据后再审</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>第 7 行</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
